--- a/news_daily/2026-09-10.xlsx
+++ b/news_daily/2026-09-10.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -4073,178 +4073,202 @@
       <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>NVIDIA and Palantir Bring Sovereign Intelligence to Critical Supply Chains</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaWc2ZTBXQVItX3JBbGVFX3J3dk9fVEpfN1FEbzBxVE5rQWJQVGc4Nnl6QnFTVTcyekJHVkNNZUtCV25EeTZYTDROVjhscm5yUXhLVFVWWXN3ZEc5Q0dNRjdRMHh4cVZkV2R0VUVVZnZ1cXUtQW5Xd2E2bGRQQjZvWlM1OWNralNJd0JvV1dWbE5VVnF6VjNtUFFNUW84cERycXVwVE9HbkdvNFJQRlE?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Newsroom</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>9750c6fb808f471c84bcce5769fbb55b</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>8aeba8e2b3ecea12d7237b7c</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>e7358190d1bebe3c142dc725</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>0.743</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaWc2ZTBXQVItX3JBbGVFX3J3dk9fVEpfN1FEbzBxVE5rQWJQVGc4Nnl6QnFTVTcyekJHVkNNZUtCV25EeTZYTDROVjhscm5yUXhLVFVWWXN3ZEc5Q0dNRjdRMHh4cVZkV2R0VUVVZnZ1cXUtQW5Xd2E2bGRQQjZvWlM1OWNralNJd0JvV1dWbE5VVnF6VjNtUFFNUW84cERycXVwVE9HbkdvNFJQRlE?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Newsroom</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>8aeba8e2b3ecea12d7237b7c</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>e7358190d1bebe3c142dc725</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr">
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC19" s="4" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF19" s="4" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG19" s="4" t="inlineStr">
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr"/>
-      <c r="BL19" s="4" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5101,1040 +5125,1184 @@
       <c r="BL24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Jabil Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Can Jabil's Supply Chain Strength Sustain Its Growth Momentum?</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.823</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZ3JKS29adHJkQ2RTVlpuSDZSZDNpZU5DRzFMVnJTZDFKNFloVWRmU255aFNKSTR4Sy12LWxfdkJTNDdqdHU5SG85dDVtS3c3R1ZLN3VWMVdyd0U2c0hiX1lCMmFrRWplQmlHeHNXTENoRVZyRmpJekZIeEx0UzRPR0pNanB0ckFtM0gyNmNzRElILVFERF9zRHQ0SEIxeDUxc2Zn?oc=5</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>ca8e05b90d1846f4aa9d7c383c60ea23</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6c90f917292086bd61f1cc46</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>cc535555c5ec1b65e311778e</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr"/>
+      <c r="AL25" s="2" t="inlineStr"/>
+      <c r="AM25" s="2" t="inlineStr"/>
+      <c r="AN25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>0.823</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZ3JKS29adHJkQ2RTVlpuSDZSZDNpZU5DRzFMVnJTZDFKNFloVWRmU255aFNKSTR4Sy12LWxfdkJTNDdqdHU5SG85dDVtS3c3R1ZLN3VWMVdyd0U2c0hiX1lCMmFrRWplQmlHeHNXTENoRVZyRmpJekZIeEx0UzRPR0pNanB0ckFtM0gyNmNzRElILVFERF9zRHQ0SEIxeDUxc2Zn?oc=5</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr"/>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z25" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="inlineStr">
-        <is>
-          <t>6c90f917292086bd61f1cc46</t>
-        </is>
-      </c>
-      <c r="AD25" s="4" t="inlineStr">
-        <is>
-          <t>cc535555c5ec1b65e311778e</t>
-        </is>
-      </c>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="inlineStr"/>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr"/>
-      <c r="AI25" s="4" t="inlineStr"/>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr"/>
-      <c r="AQ25" s="4" t="inlineStr"/>
-      <c r="AR25" s="4" t="inlineStr"/>
-      <c r="AS25" s="4" t="inlineStr"/>
-      <c r="AT25" s="4" t="inlineStr"/>
-      <c r="AU25" s="4" t="inlineStr"/>
-      <c r="AV25" s="4" t="inlineStr"/>
-      <c r="AW25" s="4" t="inlineStr">
+      <c r="AP25" s="2" t="inlineStr"/>
+      <c r="AQ25" s="2" t="inlineStr"/>
+      <c r="AR25" s="2" t="inlineStr"/>
+      <c r="AS25" s="2" t="inlineStr"/>
+      <c r="AT25" s="2" t="inlineStr"/>
+      <c r="AU25" s="2" t="inlineStr"/>
+      <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX25" s="4" t="inlineStr"/>
-      <c r="AY25" s="4" t="inlineStr"/>
-      <c r="AZ25" s="4" t="inlineStr"/>
-      <c r="BA25" s="4" t="inlineStr"/>
-      <c r="BB25" s="4" t="inlineStr">
+      <c r="AX25" s="2" t="inlineStr"/>
+      <c r="AY25" s="2" t="inlineStr"/>
+      <c r="AZ25" s="2" t="inlineStr"/>
+      <c r="BA25" s="2" t="inlineStr"/>
+      <c r="BB25" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="BC25" s="4" t="inlineStr">
+      <c r="BC25" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD25" s="4" t="inlineStr"/>
-      <c r="BE25" s="4" t="inlineStr">
+      <c r="BD25" s="2" t="inlineStr"/>
+      <c r="BE25" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF25" s="4" t="inlineStr">
+      <c r="BF25" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG25" s="4" t="inlineStr">
+      <c r="BG25" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH25" s="4" t="inlineStr"/>
-      <c r="BI25" s="4" t="inlineStr"/>
-      <c r="BJ25" s="4" t="inlineStr"/>
-      <c r="BK25" s="4" t="inlineStr"/>
-      <c r="BL25" s="4" t="inlineStr"/>
+      <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Copart, Inc.</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Copart (NASDAQ:CPRT) Stock Surges After Hours on Reported ACV Acquisition Despite Q4 EPS Miss</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOc2VmZ3E2dTJkRGxGcERpeFJTd0g5S01ocDM3UW9KbWJpN01WTmlMS2ZzVndFTkdfS1p0Q1hydV9qT3p5OUpWT184NUpXWjk3OXJ6SXVRQ0JfT0ZtSVc1SjFzZk90MXp1dmh0T0tqbzZPWkRwUmhqMGY2cUJDQTdhLXhzLUF0T2FMNktLUGFSNFFmMHFodktrdDJ3SGpFQUo2VDJBRmZwX3dzd1ZUOVcyY2pSZ3p3NER6dDZlOVIwTG1sdk9DQ09QUDlrZVFJMDl2dlBueEVDWUlzdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>ChartMill</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>EPS miss</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>8321b603bad84c769c250266a811769a</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>7a5cc749e5f60582f05530b6</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>5e973c886a6dc88dee4aeaaa</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr"/>
+      <c r="AL26" s="2" t="inlineStr"/>
+      <c r="AM26" s="2" t="inlineStr"/>
+      <c r="AN26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOc2VmZ3E2dTJkRGxGcERpeFJTd0g5S01ocDM3UW9KbWJpN01WTmlMS2ZzVndFTkdfS1p0Q1hydV9qT3p5OUpWT184NUpXWjk3OXJ6SXVRQ0JfT0ZtSVc1SjFzZk90MXp1dmh0T0tqbzZPWkRwUmhqMGY2cUJDQTdhLXhzLUF0T2FMNktLUGFSNFFmMHFodktrdDJ3SGpFQUo2VDJBRmZwX3dzd1ZUOVcyY2pSZ3p3NER6dDZlOVIwTG1sdk9DQ09QUDlrZVFJMDl2dlBueEVDWUlzdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>ChartMill</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>EPS miss</t>
-        </is>
-      </c>
-      <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="inlineStr">
-        <is>
-          <t>7a5cc749e5f60582f05530b6</t>
-        </is>
-      </c>
-      <c r="AD26" s="4" t="inlineStr">
-        <is>
-          <t>5e973c886a6dc88dee4aeaaa</t>
-        </is>
-      </c>
-      <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="inlineStr"/>
-      <c r="AG26" s="4" t="inlineStr"/>
-      <c r="AH26" s="4" t="inlineStr"/>
-      <c r="AI26" s="4" t="inlineStr"/>
-      <c r="AJ26" s="4" t="inlineStr"/>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="inlineStr"/>
-      <c r="AM26" s="4" t="inlineStr"/>
-      <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="inlineStr"/>
-      <c r="AP26" s="4" t="inlineStr"/>
-      <c r="AQ26" s="4" t="inlineStr"/>
-      <c r="AR26" s="4" t="inlineStr"/>
-      <c r="AS26" s="4" t="inlineStr"/>
-      <c r="AT26" s="4" t="inlineStr"/>
-      <c r="AU26" s="4" t="inlineStr"/>
-      <c r="AV26" s="4" t="inlineStr"/>
-      <c r="AW26" s="4" t="inlineStr">
+      <c r="AP26" s="2" t="inlineStr"/>
+      <c r="AQ26" s="2" t="inlineStr"/>
+      <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr"/>
+      <c r="AT26" s="2" t="inlineStr"/>
+      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX26" s="4" t="inlineStr"/>
-      <c r="AY26" s="4" t="inlineStr"/>
-      <c r="AZ26" s="4" t="inlineStr"/>
-      <c r="BA26" s="4" t="inlineStr"/>
-      <c r="BB26" s="4" t="inlineStr">
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr"/>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="BC26" s="4" t="inlineStr">
+      <c r="BC26" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD26" s="4" t="inlineStr"/>
-      <c r="BE26" s="4" t="inlineStr">
+      <c r="BD26" s="2" t="inlineStr"/>
+      <c r="BE26" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF26" s="4" t="inlineStr">
+      <c r="BF26" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG26" s="4" t="inlineStr">
+      <c r="BG26" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH26" s="4" t="inlineStr"/>
-      <c r="BI26" s="4" t="inlineStr"/>
-      <c r="BJ26" s="4" t="inlineStr"/>
-      <c r="BK26" s="4" t="inlineStr"/>
-      <c r="BL26" s="4" t="inlineStr"/>
+      <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Nvidia and Palantir plant a flag for sovereign AI inside 'the world's most complex supply chain'</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.236</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOZER3ZzhjRXExd2N6dXo5RUFXUFJmbzJxWnF4VmN3WlZ0RmhxZ29oNlZnZUxwc242Q2FxdFo0eGVpYXIyNlhpYUpVd0YxQXhOOV9iQUM5ZVBFREdRVUg2QTItZFhNdEFtQ25aYk1VVFF0LTRZd1FSd3RSamJ2Q2x1VDV6cEJPUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Fast Company</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>4e4ff3455ad643bd95c2bd6f92176f3a</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>98e852f3c9d3606785d2f86c</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>ffbed199495a1a7a607a4a83</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr"/>
+      <c r="AL27" s="2" t="inlineStr"/>
+      <c r="AM27" s="2" t="inlineStr"/>
+      <c r="AN27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>0.236</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOZER3ZzhjRXExd2N6dXo5RUFXUFJmbzJxWnF4VmN3WlZ0RmhxZ29oNlZnZUxwc242Q2FxdFo0eGVpYXIyNlhpYUpVd0YxQXhOOV9iQUM5ZVBFREdRVUg2QTItZFhNdEFtQ25aYk1VVFF0LTRZd1FSd3RSamJ2Q2x1VDV6cEJPUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>Fast Company</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr"/>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z27" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>98e852f3c9d3606785d2f86c</t>
-        </is>
-      </c>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>ffbed199495a1a7a607a4a83</t>
-        </is>
-      </c>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="inlineStr"/>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr"/>
-      <c r="AI27" s="4" t="inlineStr"/>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr"/>
-      <c r="AQ27" s="4" t="inlineStr"/>
-      <c r="AR27" s="4" t="inlineStr"/>
-      <c r="AS27" s="4" t="inlineStr"/>
-      <c r="AT27" s="4" t="inlineStr"/>
-      <c r="AU27" s="4" t="inlineStr"/>
-      <c r="AV27" s="4" t="inlineStr"/>
-      <c r="AW27" s="4" t="inlineStr">
+      <c r="AP27" s="2" t="inlineStr"/>
+      <c r="AQ27" s="2" t="inlineStr"/>
+      <c r="AR27" s="2" t="inlineStr"/>
+      <c r="AS27" s="2" t="inlineStr"/>
+      <c r="AT27" s="2" t="inlineStr"/>
+      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX27" s="4" t="inlineStr"/>
-      <c r="AY27" s="4" t="inlineStr"/>
-      <c r="AZ27" s="4" t="inlineStr"/>
-      <c r="BA27" s="4" t="inlineStr"/>
-      <c r="BB27" s="4" t="inlineStr">
+      <c r="AX27" s="2" t="inlineStr"/>
+      <c r="AY27" s="2" t="inlineStr"/>
+      <c r="AZ27" s="2" t="inlineStr"/>
+      <c r="BA27" s="2" t="inlineStr"/>
+      <c r="BB27" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC27" s="4" t="inlineStr">
+      <c r="BC27" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD27" s="4" t="inlineStr"/>
-      <c r="BE27" s="4" t="inlineStr">
+      <c r="BD27" s="2" t="inlineStr"/>
+      <c r="BE27" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF27" s="4" t="inlineStr">
+      <c r="BF27" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG27" s="4" t="inlineStr">
+      <c r="BG27" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH27" s="4" t="inlineStr"/>
-      <c r="BI27" s="4" t="inlineStr"/>
-      <c r="BJ27" s="4" t="inlineStr"/>
-      <c r="BK27" s="4" t="inlineStr"/>
-      <c r="BL27" s="4" t="inlineStr"/>
+      <c r="BH27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Jabil Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Jabil Procurement &amp; Supply Chain Services on Optionality</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcEFNdW5xM2JET0IzY1NRazlFRlhOdDl1YWRnazdQUG9zdkZBMGtMLXVCWTM5N3VyQ0xad0lTamVsOWVVR0ItZ3NGcXJFM0lCbGFoUFprbGRCekpsWmtzczlpc2VYT0RoeTJ2c01QYkdxaHJkOV93eU1PRldZdXpaZmdzenQ5VVBLU2ZrS3d1QXBEWnRDVWNr?oc=5</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Digital</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1a4a7216e45043f8833f580d3ff4170e</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>ca4289b6f143a10b17d97107</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>a026054f56042eb504412488</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+      <c r="AK28" s="2" t="inlineStr"/>
+      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AM28" s="2" t="inlineStr"/>
+      <c r="AN28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcEFNdW5xM2JET0IzY1NRazlFRlhOdDl1YWRnazdQUG9zdkZBMGtMLXVCWTM5N3VyQ0xad0lTamVsOWVVR0ItZ3NGcXJFM0lCbGFoUFprbGRCekpsWmtzczlpc2VYT0RoeTJ2c01QYkdxaHJkOV93eU1PRldZdXpaZmdzenQ5VVBLU2ZrS3d1QXBEWnRDVWNr?oc=5</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>Manufacturing Digital</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr"/>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>ca4289b6f143a10b17d97107</t>
-        </is>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t>a026054f56042eb504412488</t>
-        </is>
-      </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="inlineStr"/>
-      <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr"/>
-      <c r="AQ28" s="4" t="inlineStr"/>
-      <c r="AR28" s="4" t="inlineStr"/>
-      <c r="AS28" s="4" t="inlineStr"/>
-      <c r="AT28" s="4" t="inlineStr"/>
-      <c r="AU28" s="4" t="inlineStr"/>
-      <c r="AV28" s="4" t="inlineStr"/>
-      <c r="AW28" s="4" t="inlineStr">
+      <c r="AP28" s="2" t="inlineStr"/>
+      <c r="AQ28" s="2" t="inlineStr"/>
+      <c r="AR28" s="2" t="inlineStr"/>
+      <c r="AS28" s="2" t="inlineStr"/>
+      <c r="AT28" s="2" t="inlineStr"/>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX28" s="4" t="inlineStr"/>
-      <c r="AY28" s="4" t="inlineStr"/>
-      <c r="AZ28" s="4" t="inlineStr"/>
-      <c r="BA28" s="4" t="inlineStr"/>
-      <c r="BB28" s="4" t="inlineStr">
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr"/>
+      <c r="AZ28" s="2" t="inlineStr"/>
+      <c r="BA28" s="2" t="inlineStr"/>
+      <c r="BB28" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="BC28" s="4" t="inlineStr">
+      <c r="BC28" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD28" s="4" t="inlineStr"/>
-      <c r="BE28" s="4" t="inlineStr">
+      <c r="BD28" s="2" t="inlineStr"/>
+      <c r="BE28" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF28" s="4" t="inlineStr">
+      <c r="BF28" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG28" s="4" t="inlineStr">
+      <c r="BG28" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH28" s="4" t="inlineStr"/>
-      <c r="BI28" s="4" t="inlineStr"/>
-      <c r="BJ28" s="4" t="inlineStr"/>
-      <c r="BK28" s="4" t="inlineStr"/>
-      <c r="BL28" s="4" t="inlineStr"/>
+      <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>I was laid off from Amazon. After struggling to relax as a working mom, I went all in on my wellness side hustle.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>'-0.01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNeXhzNEdYazJ2Q1MteUZ6SlVyVXZDbHJNVGpaS0txR2hiaUkzWDIyaWVibkg0MGdtVDNZRERWU0w2cWJUdVE2bERZUktEVnV2b1FKUVNFUWNOaHBDS1RlT18tZV9nSmNBeXBRUUxISWZxWUxIdVpYSEZZNC1fdE9aQjVSODl5a29NRjVrT1hEdzlsNENsYnl2Tnc1SW8zbF9leC1qX0l3TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>laid off</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>06319d2578f54ddebd41cd964c083e5d</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2a5e71c9f726025cd974a828</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>2f12951d181a1fbc456b500c</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+      <c r="AK29" s="2" t="inlineStr"/>
+      <c r="AL29" s="2" t="inlineStr"/>
+      <c r="AM29" s="2" t="inlineStr"/>
+      <c r="AN29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>'-0.01</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
-      <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNeXhzNEdYazJ2Q1MteUZ6SlVyVXZDbHJNVGpaS0txR2hiaUkzWDIyaWVibkg0MGdtVDNZRERWU0w2cWJUdVE2bERZUktEVnV2b1FKUVNFUWNOaHBDS1RlT18tZV9nSmNBeXBRUUxISWZxWUxIdVpYSEZZNC1fdE9aQjVSODl5a29NRjVrT1hEdzlsNENsYnl2Tnc1SW8zbF9leC1qX0l3TQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>Business Insider</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y29" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z29" s="4" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>2a5e71c9f726025cd974a828</t>
-        </is>
-      </c>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>2f12951d181a1fbc456b500c</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="inlineStr"/>
-      <c r="AG29" s="4" t="inlineStr"/>
-      <c r="AH29" s="4" t="inlineStr"/>
-      <c r="AI29" s="4" t="inlineStr"/>
-      <c r="AJ29" s="4" t="inlineStr"/>
-      <c r="AK29" s="4" t="inlineStr"/>
-      <c r="AL29" s="4" t="inlineStr"/>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="inlineStr"/>
-      <c r="AO29" s="4" t="inlineStr"/>
-      <c r="AP29" s="4" t="inlineStr"/>
-      <c r="AQ29" s="4" t="inlineStr"/>
-      <c r="AR29" s="4" t="inlineStr"/>
-      <c r="AS29" s="4" t="inlineStr"/>
-      <c r="AT29" s="4" t="inlineStr"/>
-      <c r="AU29" s="4" t="inlineStr"/>
-      <c r="AV29" s="4" t="inlineStr"/>
-      <c r="AW29" s="4" t="inlineStr"/>
-      <c r="AX29" s="4" t="inlineStr"/>
-      <c r="AY29" s="4" t="inlineStr"/>
-      <c r="AZ29" s="4" t="inlineStr"/>
-      <c r="BA29" s="4" t="inlineStr"/>
-      <c r="BB29" s="4" t="inlineStr">
+      <c r="AP29" s="2" t="inlineStr"/>
+      <c r="AQ29" s="2" t="inlineStr"/>
+      <c r="AR29" s="2" t="inlineStr"/>
+      <c r="AS29" s="2" t="inlineStr"/>
+      <c r="AT29" s="2" t="inlineStr"/>
+      <c r="AU29" s="2" t="inlineStr"/>
+      <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" s="2" t="inlineStr"/>
+      <c r="AX29" s="2" t="inlineStr"/>
+      <c r="AY29" s="2" t="inlineStr"/>
+      <c r="AZ29" s="2" t="inlineStr"/>
+      <c r="BA29" s="2" t="inlineStr"/>
+      <c r="BB29" s="2" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC29" s="4" t="inlineStr">
+      <c r="BC29" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD29" s="4" t="inlineStr"/>
-      <c r="BE29" s="4" t="inlineStr">
+      <c r="BD29" s="2" t="inlineStr"/>
+      <c r="BE29" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF29" s="4" t="inlineStr"/>
-      <c r="BG29" s="4" t="inlineStr">
+      <c r="BF29" s="2" t="inlineStr"/>
+      <c r="BG29" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH29" s="4" t="inlineStr"/>
-      <c r="BI29" s="4" t="inlineStr"/>
-      <c r="BJ29" s="4" t="inlineStr"/>
-      <c r="BK29" s="4" t="inlineStr"/>
-      <c r="BL29" s="4" t="inlineStr"/>
+      <c r="BH29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Amgen Inc.</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>2026-09-10T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026 Amgen Irish Open format, cut rules and DP World Tour playoff format</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>'-0.029</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUlNrQ3I0NkpaZU1YbkJnMDEtTjVKbk9SQXhDQUNOZHVKQUJzMG02X3c0REFLYms2dkIwOVNkU3VHaVE2Z3d5RVp2X3ZtYnFXbGk1UlhoTnI0dkVtU2xEMHY3bFY3M2haLXVVOVVIUWt3VDBHQkYxNUJOc0xtT3duajg2UkRFOERQckdZWFJiaU1oZnR1N05YQ09UTXN2RW1RamVwUktfd0p2Y2ZLVGZXQ200Y2lSbzhia0lFNThLNllsT0FhNHctRjNvVnV4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Golf News Net</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92d283572c5449a99c3d75fc22dd18a2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>92c140fd7e6aced6c778702a</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>d2bb5f6b7bd798d00df59015</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+      <c r="AK30" s="2" t="inlineStr"/>
+      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AM30" s="2" t="inlineStr"/>
+      <c r="AN30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>'-0.029</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUlNrQ3I0NkpaZU1YbkJnMDEtTjVKbk9SQXhDQUNOZHVKQUJzMG02X3c0REFLYms2dkIwOVNkU3VHaVE2Z3d5RVp2X3ZtYnFXbGk1UlhoTnI0dkVtU2xEMHY3bFY3M2haLXVVOVVIUWt3VDBHQkYxNUJOc0xtT3duajg2UkRFOERQckdZWFJiaU1oZnR1N05YQ09UTXN2RW1RamVwUktfd0p2Y2ZLVGZXQ200Y2lSbzhia0lFNThLNllsT0FhNHctRjNvVnV4Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Golf News Net</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y30" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z30" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="inlineStr">
-        <is>
-          <t>92c140fd7e6aced6c778702a</t>
-        </is>
-      </c>
-      <c r="AD30" s="4" t="inlineStr">
-        <is>
-          <t>d2bb5f6b7bd798d00df59015</t>
-        </is>
-      </c>
-      <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" s="4" t="inlineStr"/>
-      <c r="AG30" s="4" t="inlineStr"/>
-      <c r="AH30" s="4" t="inlineStr"/>
-      <c r="AI30" s="4" t="inlineStr"/>
-      <c r="AJ30" s="4" t="inlineStr"/>
-      <c r="AK30" s="4" t="inlineStr"/>
-      <c r="AL30" s="4" t="inlineStr"/>
-      <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="inlineStr"/>
-      <c r="AO30" s="4" t="inlineStr"/>
-      <c r="AP30" s="4" t="inlineStr"/>
-      <c r="AQ30" s="4" t="inlineStr"/>
-      <c r="AR30" s="4" t="inlineStr"/>
-      <c r="AS30" s="4" t="inlineStr"/>
-      <c r="AT30" s="4" t="inlineStr"/>
-      <c r="AU30" s="4" t="inlineStr"/>
-      <c r="AV30" s="4" t="inlineStr"/>
-      <c r="AW30" s="4" t="inlineStr">
+      <c r="AP30" s="2" t="inlineStr"/>
+      <c r="AQ30" s="2" t="inlineStr"/>
+      <c r="AR30" s="2" t="inlineStr"/>
+      <c r="AS30" s="2" t="inlineStr"/>
+      <c r="AT30" s="2" t="inlineStr"/>
+      <c r="AU30" s="2" t="inlineStr"/>
+      <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX30" s="4" t="inlineStr"/>
-      <c r="AY30" s="4" t="inlineStr"/>
-      <c r="AZ30" s="4" t="inlineStr"/>
-      <c r="BA30" s="4" t="inlineStr"/>
-      <c r="BB30" s="4" t="inlineStr">
+      <c r="AX30" s="2" t="inlineStr"/>
+      <c r="AY30" s="2" t="inlineStr"/>
+      <c r="AZ30" s="2" t="inlineStr"/>
+      <c r="BA30" s="2" t="inlineStr"/>
+      <c r="BB30" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="BC30" s="4" t="inlineStr">
+      <c r="BC30" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD30" s="4" t="inlineStr"/>
-      <c r="BE30" s="4" t="inlineStr">
+      <c r="BD30" s="2" t="inlineStr"/>
+      <c r="BE30" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF30" s="4" t="inlineStr">
+      <c r="BF30" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG30" s="4" t="inlineStr">
+      <c r="BG30" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH30" s="4" t="inlineStr"/>
-      <c r="BI30" s="4" t="inlineStr"/>
-      <c r="BJ30" s="4" t="inlineStr"/>
-      <c r="BK30" s="4" t="inlineStr"/>
-      <c r="BL30" s="4" t="inlineStr"/>
+      <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -6185,13 +6353,17 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -6240,7 +6412,11 @@
         </is>
       </c>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AB31" s="4" t="inlineStr">
+        <is>
+          <t>3018c8491ead44078997133f78f8fd0f</t>
+        </is>
+      </c>
       <c r="AC31" s="4" t="inlineStr">
         <is>
           <t>2e420110141adcc76639c43f</t>
@@ -6261,7 +6437,11 @@
       <c r="AL31" s="4" t="inlineStr"/>
       <c r="AM31" s="4" t="inlineStr"/>
       <c r="AN31" s="4" t="inlineStr"/>
-      <c r="AO31" s="4" t="inlineStr"/>
+      <c r="AO31" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="4" t="inlineStr"/>
       <c r="AQ31" s="4" t="inlineStr"/>
       <c r="AR31" s="4" t="inlineStr"/>
@@ -6299,8 +6479,16 @@
       <c r="BH31" s="4" t="inlineStr"/>
       <c r="BI31" s="4" t="inlineStr"/>
       <c r="BJ31" s="4" t="inlineStr"/>
-      <c r="BK31" s="4" t="inlineStr"/>
-      <c r="BL31" s="4" t="inlineStr"/>
+      <c r="BK31" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -6351,13 +6539,17 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -6406,7 +6598,11 @@
         </is>
       </c>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>08c47fb9a97d4d0684305d3caea02db1</t>
+        </is>
+      </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
           <t>71df0bce8b8853fa13f344cf</t>
@@ -6427,7 +6623,11 @@
       <c r="AL32" s="4" t="inlineStr"/>
       <c r="AM32" s="4" t="inlineStr"/>
       <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr"/>
+      <c r="AO32" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="4" t="inlineStr"/>
       <c r="AQ32" s="4" t="inlineStr"/>
       <c r="AR32" s="4" t="inlineStr"/>
@@ -6473,8 +6673,16 @@
       <c r="BH32" s="4" t="inlineStr"/>
       <c r="BI32" s="4" t="inlineStr"/>
       <c r="BJ32" s="4" t="inlineStr"/>
-      <c r="BK32" s="4" t="inlineStr"/>
-      <c r="BL32" s="4" t="inlineStr"/>
+      <c r="BK32" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -6525,13 +6733,17 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -6580,7 +6792,11 @@
         </is>
       </c>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AB33" s="4" t="inlineStr">
+        <is>
+          <t>9ecfeb1fc3744124a0ed5191189b1420</t>
+        </is>
+      </c>
       <c r="AC33" s="4" t="inlineStr">
         <is>
           <t>dc30767166052ec009a79de0</t>
@@ -6601,7 +6817,11 @@
       <c r="AL33" s="4" t="inlineStr"/>
       <c r="AM33" s="4" t="inlineStr"/>
       <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="inlineStr"/>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="4" t="inlineStr"/>
       <c r="AQ33" s="4" t="inlineStr"/>
       <c r="AR33" s="4" t="inlineStr"/>
@@ -6647,8 +6867,16 @@
       <c r="BH33" s="4" t="inlineStr"/>
       <c r="BI33" s="4" t="inlineStr"/>
       <c r="BJ33" s="4" t="inlineStr"/>
-      <c r="BK33" s="4" t="inlineStr"/>
-      <c r="BL33" s="4" t="inlineStr"/>
+      <c r="BK33" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6836,7 +7064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL24"/>
+  <dimension ref="A1:BL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9722,12 +9950,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -9737,7 +9965,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA and Palantir Bring Sovereign Intelligence to Critical Supply Chains</t>
+          <t>Cisco FMC bugs exploited by nation-state and ransomware actors (CVE-2026-20079, CVE-2026-20316)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -9748,7 +9976,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>資安攻擊</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -9758,13 +9986,17 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -9774,7 +10006,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>'-0.572</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr"/>
@@ -9788,40 +10020,44 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaWc2ZTBXQVItX3JBbGVFX3J3dk9fVEpfN1FEbzBxVE5rQWJQVGc4Nnl6QnFTVTcyekJHVkNNZUtCV25EeTZYTDROVjhscm5yUXhLVFVWWXN3ZEc5Q0dNRjdRMHh4cVZkV2R0VUVVZnZ1cXUtQW5Xd2E2bGRQQjZvWlM1OWNralNJd0JvV1dWbE5VVnF6VjNtUFFNUW84cERycXVwVE9HbkdvNFJQRlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPMjByVURZOGVMVzAwUVNaa01tNlNVMTE0ei1JWllyc3NibWc5N1RLNnJJbGtDOXd0bDVUalZ6bTdvbmhFQ3NZVzNJcDJmZHFINGsydUZiTk1PcE5nYllrS2J1TS0yOFp2WVFyZldkcW02NHdja3ZCX0hsclBralNlUXNfVFV3Z2F0YVo4cmgwR1BkdjNyUjlDUw?oc=5</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA Newsroom</t>
+          <t>Help Net Security</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>CYBER_ATTACK</t>
         </is>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>supply chain</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>3018c8491ead44078997133f78f8fd0f</t>
+        </is>
+      </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>8aeba8e2b3ecea12d7237b7c</t>
+          <t>2e420110141adcc76639c43f</t>
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>e7358190d1bebe3c142dc725</t>
+          <t>6d8450cf1d2478dab7cfdd9a</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr"/>
@@ -9834,7 +10070,11 @@
       <c r="AL15" s="4" t="inlineStr"/>
       <c r="AM15" s="4" t="inlineStr"/>
       <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="4" t="inlineStr"/>
       <c r="AQ15" s="4" t="inlineStr"/>
       <c r="AR15" s="4" t="inlineStr"/>
@@ -9842,18 +10082,14 @@
       <c r="AT15" s="4" t="inlineStr"/>
       <c r="AU15" s="4" t="inlineStr"/>
       <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW15" s="4" t="inlineStr"/>
       <c r="AX15" s="4" t="inlineStr"/>
       <c r="AY15" s="4" t="inlineStr"/>
       <c r="AZ15" s="4" t="inlineStr"/>
       <c r="BA15" s="4" t="inlineStr"/>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="BC15" s="4" t="inlineStr">
@@ -9864,24 +10100,28 @@
       <c r="BD15" s="4" t="inlineStr"/>
       <c r="BE15" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF15" s="4" t="inlineStr"/>
       <c r="BG15" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH15" s="4" t="inlineStr"/>
       <c r="BI15" s="4" t="inlineStr"/>
       <c r="BJ15" s="4" t="inlineStr"/>
-      <c r="BK15" s="4" t="inlineStr"/>
-      <c r="BL15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -9896,12 +10136,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Jabil Inc. Common Stock</t>
+          <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -9911,7 +10151,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Can Jabil's Supply Chain Strength Sustain Its Growth Momentum?</t>
+          <t>Tyson Foods at Barclays conference: guidance cut, brands in focus</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -9922,7 +10162,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>財測下修</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -9932,13 +10172,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -9948,7 +10192,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>'-0.754</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr"/>
@@ -9962,40 +10206,44 @@
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZ3JKS29adHJkQ2RTVlpuSDZSZDNpZU5DRzFMVnJTZDFKNFloVWRmU255aFNKSTR4Sy12LWxfdkJTNDdqdHU5SG85dDVtS3c3R1ZLN3VWMVdyd0U2c0hiX1lCMmFrRWplQmlHeHNXTENoRVZyRmpJekZIeEx0UzRPR0pNanB0ckFtM0gyNmNzRElILVFERF9zRHQ0SEIxeDUxc2Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOMHNJWGdad2RJLWdfci1sakh1dy0zNVBOenAxc05yeVFJWXZrSTlyVUY0VEpqMXBvT01ObTJEOVNMSXJiV0FJNHdqdGRqZ2xfTXRzck1iTmJOeVczb3BPZmktVHp0T21mcUlKb1loOGZuZmhCaUVIX2Z6elZtUzVoU2JTWVhoXzUzcFFydHJHUi1JN1JpcWtyLWJ1dEJKSGJtLW1VRHpLX2pyRjRnbU00TEJOUVdURE1HUjNz?oc=5</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>EARNINGS_WARNING</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>supply chain</t>
+          <t>guidance cut</t>
         </is>
       </c>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>08c47fb9a97d4d0684305d3caea02db1</t>
+        </is>
+      </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
-          <t>6c90f917292086bd61f1cc46</t>
+          <t>71df0bce8b8853fa13f344cf</t>
         </is>
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>cc535555c5ec1b65e311778e</t>
+          <t>b71f865e8b6c82f59ac215c5</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr"/>
@@ -10008,7 +10256,11 @@
       <c r="AL16" s="4" t="inlineStr"/>
       <c r="AM16" s="4" t="inlineStr"/>
       <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
       <c r="AR16" s="4" t="inlineStr"/>
@@ -10027,7 +10279,7 @@
       <c r="BA16" s="4" t="inlineStr"/>
       <c r="BB16" s="4" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="BC16" s="4" t="inlineStr">
@@ -10054,8 +10306,16 @@
       <c r="BH16" s="4" t="inlineStr"/>
       <c r="BI16" s="4" t="inlineStr"/>
       <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10070,12 +10330,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -10085,7 +10345,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Copart (NASDAQ:CPRT) Stock Surges After Hours on Reported ACV Acquisition Despite Q4 EPS Miss</t>
+          <t>Uber's CEO says you could see lower ride prices as a result of its layoffs</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -10096,7 +10356,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -10106,13 +10366,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -10122,7 +10386,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>'-0.875</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
@@ -10136,40 +10400,44 @@
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOc2VmZ3E2dTJkRGxGcERpeFJTd0g5S01ocDM3UW9KbWJpN01WTmlMS2ZzVndFTkdfS1p0Q1hydV9qT3p5OUpWT184NUpXWjk3OXJ6SXVRQ0JfT0ZtSVc1SjFzZk90MXp1dmh0T0tqbzZPWkRwUmhqMGY2cUJDQTdhLXhzLUF0T2FMNktLUGFSNFFmMHFodktrdDJ3SGpFQUo2VDJBRmZwX3dzd1ZUOVcyY2pSZ3p3NER6dDZlOVIwTG1sdk9DQ09QUDlrZVFJMDl2dlBueEVDWUlzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNODBUMFYxaW1DWU9EN0EyN2xkSDZxVVJGbklDOXQzTVVEYTRCU3hKMVBKWWs5QkRBTEVJZ2RKQVpCeVV3LUpKamlGblh3VzRqLXFUR2VPVnFtODRZX3hSektSb3VqamVPcWtiUGRLNVdXR29CTmxrVWp3WDJtdmZIRS01S3hlQQ?oc=5</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>ChartMill</t>
+          <t>Business Insider</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y17" s="4" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z17" s="4" t="inlineStr">
         <is>
-          <t>EPS miss</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>9ecfeb1fc3744124a0ed5191189b1420</t>
+        </is>
+      </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
-          <t>7a5cc749e5f60582f05530b6</t>
+          <t>dc30767166052ec009a79de0</t>
         </is>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>5e973c886a6dc88dee4aeaaa</t>
+          <t>073205007eaa439a7925f40b</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr"/>
@@ -10182,7 +10450,11 @@
       <c r="AL17" s="4" t="inlineStr"/>
       <c r="AM17" s="4" t="inlineStr"/>
       <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="inlineStr"/>
       <c r="AQ17" s="4" t="inlineStr"/>
       <c r="AR17" s="4" t="inlineStr"/>
@@ -10192,7 +10464,7 @@
       <c r="AV17" s="4" t="inlineStr"/>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr"/>
@@ -10201,7 +10473,7 @@
       <c r="BA17" s="4" t="inlineStr"/>
       <c r="BB17" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="BC17" s="4" t="inlineStr">
@@ -10212,12 +10484,12 @@
       <c r="BD17" s="4" t="inlineStr"/>
       <c r="BE17" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG17" s="4" t="inlineStr">
@@ -10228,1213 +10500,19 @@
       <c r="BH17" s="4" t="inlineStr"/>
       <c r="BI17" s="4" t="inlineStr"/>
       <c r="BJ17" s="4" t="inlineStr"/>
-      <c r="BK17" s="4" t="inlineStr"/>
-      <c r="BL17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Nvidia and Palantir plant a flag for sovereign AI inside 'the world's most complex supply chain'</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.236</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOZER3ZzhjRXExd2N6dXo5RUFXUFJmbzJxWnF4VmN3WlZ0RmhxZ29oNlZnZUxwc242Q2FxdFo0eGVpYXIyNlhpYUpVd0YxQXhOOV9iQUM5ZVBFREdRVUg2QTItZFhNdEFtQ25aYk1VVFF0LTRZd1FSd3RSamJ2Q2x1VDV6cEJPUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Fast Company</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>98e852f3c9d3606785d2f86c</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>ffbed199495a1a7a607a4a83</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH18" s="4" t="inlineStr"/>
-      <c r="BI18" s="4" t="inlineStr"/>
-      <c r="BJ18" s="4" t="inlineStr"/>
-      <c r="BK18" s="4" t="inlineStr"/>
-      <c r="BL18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Jabil Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Jabil Procurement &amp; Supply Chain Services on Optionality</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcEFNdW5xM2JET0IzY1NRazlFRlhOdDl1YWRnazdQUG9zdkZBMGtMLXVCWTM5N3VyQ0xad0lTamVsOWVVR0ItZ3NGcXJFM0lCbGFoUFprbGRCekpsWmtzczlpc2VYT0RoeTJ2c01QYkdxaHJkOV93eU1PRldZdXpaZmdzenQ5VVBLU2ZrS3d1QXBEWnRDVWNr?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>Manufacturing Digital</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>ca4289b6f143a10b17d97107</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>a026054f56042eb504412488</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="BC19" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG19" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr"/>
-      <c r="BL19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>I was laid off from Amazon. After struggling to relax as a working mom, I went all in on my wellness side hustle.</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>'-0.01</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNeXhzNEdYazJ2Q1MteUZ6SlVyVXZDbHJNVGpaS0txR2hiaUkzWDIyaWVibkg0MGdtVDNZRERWU0w2cWJUdVE2bERZUktEVnV2b1FKUVNFUWNOaHBDS1RlT18tZV9nSmNBeXBRUUxISWZxWUxIdVpYSEZZNC1fdE9aQjVSODl5a29NRjVrT1hEdzlsNENsYnl2Tnc1SW8zbF9leC1qX0l3TQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>Business Insider</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>2a5e71c9f726025cd974a828</t>
-        </is>
-      </c>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t>2f12951d181a1fbc456b500c</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr"/>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr"/>
-      <c r="AX20" s="4" t="inlineStr"/>
-      <c r="AY20" s="4" t="inlineStr"/>
-      <c r="AZ20" s="4" t="inlineStr"/>
-      <c r="BA20" s="4" t="inlineStr"/>
-      <c r="BB20" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC20" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="4" t="inlineStr"/>
-      <c r="BE20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="inlineStr"/>
-      <c r="BG20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH20" s="4" t="inlineStr"/>
-      <c r="BI20" s="4" t="inlineStr"/>
-      <c r="BJ20" s="4" t="inlineStr"/>
-      <c r="BK20" s="4" t="inlineStr"/>
-      <c r="BL20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Amgen Inc.</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2026 Amgen Irish Open format, cut rules and DP World Tour playoff format</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>'-0.029</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUlNrQ3I0NkpaZU1YbkJnMDEtTjVKbk9SQXhDQUNOZHVKQUJzMG02X3c0REFLYms2dkIwOVNkU3VHaVE2Z3d5RVp2X3ZtYnFXbGk1UlhoTnI0dkVtU2xEMHY3bFY3M2haLXVVOVVIUWt3VDBHQkYxNUJOc0xtT3duajg2UkRFOERQckdZWFJiaU1oZnR1N05YQ09UTXN2RW1RamVwUktfd0p2Y2ZLVGZXQ200Y2lSbzhia0lFNThLNllsT0FhNHctRjNvVnV4Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>Golf News Net</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>92c140fd7e6aced6c778702a</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>d2bb5f6b7bd798d00df59015</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="BC21" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH21" s="4" t="inlineStr"/>
-      <c r="BI21" s="4" t="inlineStr"/>
-      <c r="BJ21" s="4" t="inlineStr"/>
-      <c r="BK21" s="4" t="inlineStr"/>
-      <c r="BL21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Cisco FMC bugs exploited by nation-state and ransomware actors (CVE-2026-20079, CVE-2026-20316)</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>資安攻擊</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>'-0.572</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPMjByVURZOGVMVzAwUVNaa01tNlNVMTE0ei1JWllyc3NibWc5N1RLNnJJbGtDOXd0bDVUalZ6bTdvbmhFQ3NZVzNJcDJmZHFINGsydUZiTk1PcE5nYllrS2J1TS0yOFp2WVFyZldkcW02NHdja3ZCX0hsclBralNlUXNfVFV3Z2F0YVo4cmgwR1BkdjNyUjlDUw?oc=5</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>Help Net Security</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>CYBER_ATTACK</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>ransomware</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>2e420110141adcc76639c43f</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>6d8450cf1d2478dab7cfdd9a</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr"/>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
-      <c r="AX22" s="4" t="inlineStr"/>
-      <c r="AY22" s="4" t="inlineStr"/>
-      <c r="AZ22" s="4" t="inlineStr"/>
-      <c r="BA22" s="4" t="inlineStr"/>
-      <c r="BB22" s="4" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BC22" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD22" s="4" t="inlineStr"/>
-      <c r="BE22" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF22" s="4" t="inlineStr"/>
-      <c r="BG22" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH22" s="4" t="inlineStr"/>
-      <c r="BI22" s="4" t="inlineStr"/>
-      <c r="BJ22" s="4" t="inlineStr"/>
-      <c r="BK22" s="4" t="inlineStr"/>
-      <c r="BL22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Tyson Foods, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Tyson Foods at Barclays conference: guidance cut, brands in focus</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>'-0.754</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOMHNJWGdad2RJLWdfci1sakh1dy0zNVBOenAxc05yeVFJWXZrSTlyVUY0VEpqMXBvT01ObTJEOVNMSXJiV0FJNHdqdGRqZ2xfTXRzck1iTmJOeVczb3BPZmktVHp0T21mcUlKb1loOGZuZmhCaUVIX2Z6elZtUzVoU2JTWVhoXzUzcFFydHJHUi1JN1JpcWtyLWJ1dEJKSGJtLW1VRHpLX2pyRjRnbU00TEJOUVdURE1HUjNz?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>Investing.com</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr"/>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>guidance cut</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>71df0bce8b8853fa13f344cf</t>
-        </is>
-      </c>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>b71f865e8b6c82f59ac215c5</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr"/>
-      <c r="AG23" s="4" t="inlineStr"/>
-      <c r="AH23" s="4" t="inlineStr"/>
-      <c r="AI23" s="4" t="inlineStr"/>
-      <c r="AJ23" s="4" t="inlineStr"/>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="inlineStr"/>
-      <c r="AM23" s="4" t="inlineStr"/>
-      <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr"/>
-      <c r="AQ23" s="4" t="inlineStr"/>
-      <c r="AR23" s="4" t="inlineStr"/>
-      <c r="AS23" s="4" t="inlineStr"/>
-      <c r="AT23" s="4" t="inlineStr"/>
-      <c r="AU23" s="4" t="inlineStr"/>
-      <c r="AV23" s="4" t="inlineStr"/>
-      <c r="AW23" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX23" s="4" t="inlineStr"/>
-      <c r="AY23" s="4" t="inlineStr"/>
-      <c r="AZ23" s="4" t="inlineStr"/>
-      <c r="BA23" s="4" t="inlineStr"/>
-      <c r="BB23" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC23" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD23" s="4" t="inlineStr"/>
-      <c r="BE23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG23" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH23" s="4" t="inlineStr"/>
-      <c r="BI23" s="4" t="inlineStr"/>
-      <c r="BJ23" s="4" t="inlineStr"/>
-      <c r="BK23" s="4" t="inlineStr"/>
-      <c r="BL23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Uber's CEO says you could see lower ride prices as a result of its layoffs</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>'-0.875</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNODBUMFYxaW1DWU9EN0EyN2xkSDZxVVJGbklDOXQzTVVEYTRCU3hKMVBKWWs5QkRBTEVJZ2RKQVpCeVV3LUpKamlGblh3VzRqLXFUR2VPVnFtODRZX3hSektSb3VqamVPcWtiUGRLNVdXR29CTmxrVWp3WDJtdmZIRS01S3hlQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Business Insider</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>dc30767166052ec009a79de0</t>
-        </is>
-      </c>
-      <c r="AD24" s="4" t="inlineStr">
-        <is>
-          <t>073205007eaa439a7925f40b</t>
-        </is>
-      </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr"/>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr"/>
-      <c r="AI24" s="4" t="inlineStr"/>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr"/>
-      <c r="AQ24" s="4" t="inlineStr"/>
-      <c r="AR24" s="4" t="inlineStr"/>
-      <c r="AS24" s="4" t="inlineStr"/>
-      <c r="AT24" s="4" t="inlineStr"/>
-      <c r="AU24" s="4" t="inlineStr"/>
-      <c r="AV24" s="4" t="inlineStr"/>
-      <c r="AW24" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX24" s="4" t="inlineStr"/>
-      <c r="AY24" s="4" t="inlineStr"/>
-      <c r="AZ24" s="4" t="inlineStr"/>
-      <c r="BA24" s="4" t="inlineStr"/>
-      <c r="BB24" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC24" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD24" s="4" t="inlineStr"/>
-      <c r="BE24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG24" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH24" s="4" t="inlineStr"/>
-      <c r="BI24" s="4" t="inlineStr"/>
-      <c r="BJ24" s="4" t="inlineStr"/>
-      <c r="BK24" s="4" t="inlineStr"/>
-      <c r="BL24" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL24"/>
+  <autoFilter ref="A1:BL17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-10.xlsx
+++ b/news_daily/2026-09-10.xlsx
@@ -3773,13 +3773,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3828,7 +3832,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>3e489b137d3a4d66adc045779575bcd2</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>be6b78f16a665c15c4dacfa4</t>
@@ -3849,7 +3857,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3895,8 +3907,16 @@
       <c r="BH17" s="2" t="inlineStr"/>
       <c r="BI17" s="2" t="inlineStr"/>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3947,13 +3967,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4002,7 +4026,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2d8155a755724cdcb8ae60263cf944bd</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>43bcda9431ff8f77b40eefe3</t>
@@ -4023,7 +4051,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4069,8 +4101,16 @@
       <c r="BH18" s="2" t="inlineStr"/>
       <c r="BI18" s="2" t="inlineStr"/>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4304,28 +4344,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4365,7 +4409,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4374,7 +4418,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>d77d4b03ac574cd9acb7747ba492c74c</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>93c4504e93902fc7c8413c43</t>
@@ -4395,7 +4443,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4431,10 +4483,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4470,28 +4534,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4531,7 +4599,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4540,7 +4608,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>fa634745870e407fb0a7a5d9cf53bc06</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>69b9059c16cfde92bed6fdf2</t>
@@ -4561,7 +4633,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4605,10 +4681,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4644,28 +4732,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4705,7 +4797,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4714,7 +4806,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>19233555fbbf4ff892e29e5bf0c83f18</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>c30911759654c41f1f956c9e</t>
@@ -4735,7 +4831,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4779,10 +4879,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4818,28 +4930,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4879,7 +4995,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4888,7 +5004,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>e58c3162784e432f88737d2e0e6a84d7</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>c30911759654c41f1f956c9e</t>
@@ -4909,7 +5029,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -4953,10 +5077,22 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4992,28 +5128,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5053,7 +5193,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5062,7 +5202,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>7987f2b5f8444d02a6f27d586316f5ad</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>878bd7e9cf73fc0b9a340af9</t>
@@ -5083,7 +5227,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -5119,10 +5267,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6927,13 +7087,17 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6982,7 +7146,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>04b34d2c36c044b5a54b479765720936</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>4d90a2c99fa300ffbf86c98d</t>
@@ -7003,7 +7171,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -7049,8 +7221,16 @@
       <c r="BH34" s="2" t="inlineStr"/>
       <c r="BI34" s="2" t="inlineStr"/>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL34"/>
